--- a/venta.xlsx
+++ b/venta.xlsx
@@ -6559,34 +6559,84 @@
       </c>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="B782" s="7"/>
+      <c r="A782" s="3">
+        <v>46072.0</v>
+      </c>
+      <c r="B782" s="6">
+        <v>1840.0</v>
+      </c>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="B783" s="7"/>
+      <c r="A783" s="3">
+        <v>46073.0</v>
+      </c>
+      <c r="B783" s="6">
+        <v>4157.0</v>
+      </c>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="B784" s="7"/>
+      <c r="A784" s="3">
+        <v>46074.0</v>
+      </c>
+      <c r="B784" s="6">
+        <v>4388.75</v>
+      </c>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="B785" s="7"/>
+      <c r="A785" s="3">
+        <v>46075.0</v>
+      </c>
+      <c r="B785" s="6">
+        <v>3379.23</v>
+      </c>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="B786" s="7"/>
+      <c r="A786" s="3">
+        <v>46076.0</v>
+      </c>
+      <c r="B786" s="6">
+        <v>1341.0</v>
+      </c>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="B787" s="7"/>
+      <c r="A787" s="3">
+        <v>46077.0</v>
+      </c>
+      <c r="B787" s="6">
+        <v>1634.14</v>
+      </c>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="B788" s="7"/>
+      <c r="A788" s="3">
+        <v>46078.0</v>
+      </c>
+      <c r="B788" s="6">
+        <v>1587.1</v>
+      </c>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="B789" s="7"/>
+      <c r="A789" s="3">
+        <v>46079.0</v>
+      </c>
+      <c r="B789" s="6">
+        <v>2047.86</v>
+      </c>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="B790" s="7"/>
+      <c r="A790" s="3">
+        <v>46080.0</v>
+      </c>
+      <c r="B790" s="6">
+        <v>4384.0</v>
+      </c>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="B791" s="7"/>
+      <c r="A791" s="3">
+        <v>46081.0</v>
+      </c>
+      <c r="B791" s="6">
+        <v>4716.0</v>
+      </c>
     </row>
     <row r="792" ht="15.75" customHeight="1">
       <c r="B792" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -6639,22 +6639,52 @@
       </c>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="B792" s="7"/>
+      <c r="A792" s="3">
+        <v>46082.0</v>
+      </c>
+      <c r="B792" s="6">
+        <v>3118.0</v>
+      </c>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="B793" s="7"/>
+      <c r="A793" s="3">
+        <v>46083.0</v>
+      </c>
+      <c r="B793" s="6">
+        <v>1487.0</v>
+      </c>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="B794" s="7"/>
+      <c r="A794" s="3">
+        <v>46084.0</v>
+      </c>
+      <c r="B794" s="6">
+        <v>2808.0</v>
+      </c>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="B795" s="7"/>
+      <c r="A795" s="3">
+        <v>46085.0</v>
+      </c>
+      <c r="B795" s="6">
+        <v>1404.0</v>
+      </c>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="B796" s="7"/>
+      <c r="A796" s="3">
+        <v>46086.0</v>
+      </c>
+      <c r="B796" s="6">
+        <v>1957.0</v>
+      </c>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="B797" s="7"/>
+      <c r="A797" s="3">
+        <v>46087.0</v>
+      </c>
+      <c r="B797" s="6">
+        <v>4339.0</v>
+      </c>
     </row>
     <row r="798" ht="15.75" customHeight="1">
       <c r="B798" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -6687,177 +6687,464 @@
       </c>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="B798" s="7"/>
+      <c r="A798" s="3">
+        <v>46088.0</v>
+      </c>
+      <c r="B798" s="6">
+        <v>4262.0</v>
+      </c>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="B799" s="7"/>
+      <c r="A799" s="3">
+        <v>46089.0</v>
+      </c>
+      <c r="B799" s="6">
+        <v>3370.0</v>
+      </c>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="B800" s="7"/>
+      <c r="A800" s="3">
+        <v>46090.0</v>
+      </c>
+      <c r="B800" s="6">
+        <v>1642.0</v>
+      </c>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="B801" s="7"/>
+      <c r="A801" s="3">
+        <v>46091.0</v>
+      </c>
+      <c r="B801" s="6">
+        <v>2446.0</v>
+      </c>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="B802" s="7"/>
+      <c r="A802" s="3">
+        <v>46092.0</v>
+      </c>
+      <c r="B802" s="6">
+        <v>1457.0</v>
+      </c>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="B803" s="7"/>
+      <c r="A803" s="3">
+        <v>46093.0</v>
+      </c>
+      <c r="B803" s="6">
+        <v>1846.0</v>
+      </c>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="B804" s="7"/>
+      <c r="A804" s="3">
+        <v>46094.0</v>
+      </c>
+      <c r="B804" s="6">
+        <v>3478.0</v>
+      </c>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="B805" s="7"/>
+      <c r="A805" s="3">
+        <v>46095.0</v>
+      </c>
+      <c r="B805" s="6">
+        <v>3836.0</v>
+      </c>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="B806" s="7"/>
+      <c r="A806" s="3">
+        <v>46096.0</v>
+      </c>
+      <c r="B806" s="6">
+        <v>2791.0</v>
+      </c>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="B807" s="7"/>
+      <c r="A807" s="3">
+        <v>46097.0</v>
+      </c>
+      <c r="B807" s="6">
+        <v>1302.0</v>
+      </c>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="B808" s="7"/>
+      <c r="A808" s="3">
+        <v>46098.0</v>
+      </c>
+      <c r="B808" s="6">
+        <v>2126.0</v>
+      </c>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="B809" s="7"/>
+      <c r="A809" s="3">
+        <v>46099.0</v>
+      </c>
+      <c r="B809" s="6">
+        <v>1701.0</v>
+      </c>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="B810" s="7"/>
+      <c r="A810" s="3">
+        <v>46100.0</v>
+      </c>
+      <c r="B810" s="6">
+        <v>4090.0</v>
+      </c>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="B811" s="7"/>
+      <c r="A811" s="3">
+        <v>46101.0</v>
+      </c>
+      <c r="B811" s="6">
+        <v>3793.0</v>
+      </c>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="B812" s="7"/>
+      <c r="A812" s="3">
+        <v>46102.0</v>
+      </c>
+      <c r="B812" s="6">
+        <v>4367.0</v>
+      </c>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="B813" s="7"/>
+      <c r="A813" s="3">
+        <v>46103.0</v>
+      </c>
+      <c r="B813" s="6">
+        <v>3719.0</v>
+      </c>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="B814" s="7"/>
+      <c r="A814" s="3">
+        <v>46104.0</v>
+      </c>
+      <c r="B814" s="6">
+        <v>1294.0</v>
+      </c>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="B815" s="7"/>
+      <c r="A815" s="3">
+        <v>46105.0</v>
+      </c>
+      <c r="B815" s="6">
+        <v>2092.0</v>
+      </c>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="B816" s="7"/>
+      <c r="A816" s="3">
+        <v>46106.0</v>
+      </c>
+      <c r="B816" s="6">
+        <v>1778.0</v>
+      </c>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="B817" s="7"/>
+      <c r="A817" s="3">
+        <v>46107.0</v>
+      </c>
+      <c r="B817" s="6">
+        <v>2461.0</v>
+      </c>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="B818" s="7"/>
+      <c r="A818" s="3">
+        <v>46108.0</v>
+      </c>
+      <c r="B818" s="6">
+        <v>4089.0</v>
+      </c>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="B819" s="7"/>
+      <c r="A819" s="3">
+        <v>46109.0</v>
+      </c>
+      <c r="B819" s="6">
+        <v>3038.0</v>
+      </c>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="B820" s="7"/>
+      <c r="A820" s="3">
+        <v>46110.0</v>
+      </c>
+      <c r="B820" s="6">
+        <v>3775.0</v>
+      </c>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="B821" s="7"/>
+      <c r="A821" s="3">
+        <v>46111.0</v>
+      </c>
+      <c r="B821" s="6">
+        <v>2417.0</v>
+      </c>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="B822" s="7"/>
+      <c r="A822" s="3">
+        <v>46112.0</v>
+      </c>
+      <c r="B822" s="6">
+        <v>2916.0</v>
+      </c>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="B823" s="7"/>
+      <c r="A823" s="3">
+        <v>46113.0</v>
+      </c>
+      <c r="B823" s="6">
+        <v>2600.0</v>
+      </c>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="B824" s="7"/>
+      <c r="A824" s="3">
+        <v>46114.0</v>
+      </c>
+      <c r="B824" s="6">
+        <v>2751.0</v>
+      </c>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="B825" s="7"/>
+      <c r="A825" s="3">
+        <v>46115.0</v>
+      </c>
+      <c r="B825" s="6">
+        <v>4769.0</v>
+      </c>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="B826" s="7"/>
+      <c r="A826" s="3">
+        <v>46116.0</v>
+      </c>
+      <c r="B826" s="6">
+        <v>3780.0</v>
+      </c>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="B827" s="7"/>
+      <c r="A827" s="3">
+        <v>46117.0</v>
+      </c>
+      <c r="B827" s="6">
+        <v>3827.0</v>
+      </c>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="B828" s="7"/>
+      <c r="A828" s="3">
+        <v>46118.0</v>
+      </c>
+      <c r="B828" s="6">
+        <v>3431.0</v>
+      </c>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="B829" s="7"/>
+      <c r="A829" s="3">
+        <v>46119.0</v>
+      </c>
+      <c r="B829" s="6">
+        <v>1582.0</v>
+      </c>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="B830" s="7"/>
+      <c r="A830" s="3">
+        <v>46120.0</v>
+      </c>
+      <c r="B830" s="6">
+        <v>1896.0</v>
+      </c>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="B831" s="7"/>
+      <c r="A831" s="3">
+        <v>46121.0</v>
+      </c>
+      <c r="B831" s="6">
+        <v>1333.0</v>
+      </c>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="B832" s="7"/>
+      <c r="A832" s="3">
+        <v>46122.0</v>
+      </c>
+      <c r="B832" s="6">
+        <v>3373.0</v>
+      </c>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="B833" s="7"/>
+      <c r="A833" s="3">
+        <v>46123.0</v>
+      </c>
+      <c r="B833" s="6">
+        <v>4034.0</v>
+      </c>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="B834" s="7"/>
+      <c r="A834" s="3">
+        <v>46124.0</v>
+      </c>
+      <c r="B834" s="6">
+        <v>2945.0</v>
+      </c>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="B835" s="7"/>
+      <c r="A835" s="3">
+        <v>46125.0</v>
+      </c>
+      <c r="B835" s="6">
+        <v>1136.0</v>
+      </c>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="B836" s="7"/>
+      <c r="A836" s="3">
+        <v>46126.0</v>
+      </c>
+      <c r="B836" s="6">
+        <v>2450.0</v>
+      </c>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="B837" s="7"/>
+      <c r="A837" s="3">
+        <v>46127.0</v>
+      </c>
+      <c r="B837" s="6">
+        <v>1881.0</v>
+      </c>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="B838" s="7"/>
+      <c r="A838" s="3">
+        <v>46128.0</v>
+      </c>
+      <c r="B838" s="6">
+        <v>2207.0</v>
+      </c>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="B839" s="7"/>
+      <c r="A839" s="3">
+        <v>46129.0</v>
+      </c>
+      <c r="B839" s="6">
+        <v>4065.0</v>
+      </c>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="B840" s="7"/>
+      <c r="A840" s="3">
+        <v>46130.0</v>
+      </c>
+      <c r="B840" s="6">
+        <v>3305.0</v>
+      </c>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="B841" s="7"/>
+      <c r="A841" s="3">
+        <v>46131.0</v>
+      </c>
+      <c r="B841" s="6">
+        <v>2710.0</v>
+      </c>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="B842" s="7"/>
+      <c r="A842" s="3">
+        <v>46132.0</v>
+      </c>
+      <c r="B842" s="6">
+        <v>1274.0</v>
+      </c>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="B843" s="7"/>
+      <c r="A843" s="3">
+        <v>46133.0</v>
+      </c>
+      <c r="B843" s="6">
+        <v>1619.0</v>
+      </c>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="B844" s="7"/>
+      <c r="A844" s="3">
+        <v>46134.0</v>
+      </c>
+      <c r="B844" s="6">
+        <v>1900.0</v>
+      </c>
+      <c r="D844" s="6"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="B845" s="7"/>
+      <c r="A845" s="3">
+        <v>46135.0</v>
+      </c>
+      <c r="B845" s="6">
+        <v>2654.0</v>
+      </c>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="B846" s="7"/>
+      <c r="A846" s="3">
+        <v>46136.0</v>
+      </c>
+      <c r="B846" s="6">
+        <v>4298.0</v>
+      </c>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="B847" s="7"/>
+      <c r="A847" s="3">
+        <v>46137.0</v>
+      </c>
+      <c r="B847" s="6">
+        <v>3325.0</v>
+      </c>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="B848" s="7"/>
+      <c r="A848" s="3">
+        <v>46138.0</v>
+      </c>
+      <c r="B848" s="6">
+        <v>2625.0</v>
+      </c>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="B849" s="7"/>
+      <c r="A849" s="3">
+        <v>46139.0</v>
+      </c>
+      <c r="B849" s="6">
+        <v>942.0</v>
+      </c>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="B850" s="7"/>
+      <c r="A850" s="3">
+        <v>46140.0</v>
+      </c>
+      <c r="B850" s="6">
+        <v>1898.0</v>
+      </c>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="B851" s="7"/>
+      <c r="A851" s="3">
+        <v>46141.0</v>
+      </c>
+      <c r="B851" s="6">
+        <v>2140.0</v>
+      </c>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="B852" s="7"/>
+      <c r="A852" s="3">
+        <v>46142.0</v>
+      </c>
+      <c r="B852" s="6">
+        <v>3712.0</v>
+      </c>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="B853" s="7"/>
+      <c r="A853" s="3">
+        <v>46143.0</v>
+      </c>
+      <c r="B853" s="6">
+        <v>4968.0</v>
+      </c>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="B854" s="7"/>
+      <c r="A854" s="3">
+        <v>46144.0</v>
+      </c>
+      <c r="B854" s="6">
+        <v>3975.0</v>
+      </c>
     </row>
     <row r="855" ht="15.75" customHeight="1">
+      <c r="A855" s="3"/>
       <c r="B855" s="7"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7144,28 +7144,63 @@
       </c>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="3"/>
-      <c r="B855" s="7"/>
+      <c r="A855" s="3">
+        <v>46145.0</v>
+      </c>
+      <c r="B855" s="6">
+        <v>3748.0</v>
+      </c>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="B856" s="7"/>
+      <c r="A856" s="3">
+        <v>46146.0</v>
+      </c>
+      <c r="B856" s="6">
+        <v>1925.0</v>
+      </c>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="B857" s="7"/>
+      <c r="A857" s="3">
+        <v>46147.0</v>
+      </c>
+      <c r="B857" s="6">
+        <v>1863.0</v>
+      </c>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="B858" s="7"/>
+      <c r="A858" s="3">
+        <v>46148.0</v>
+      </c>
+      <c r="B858" s="6">
+        <v>1978.0</v>
+      </c>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="B859" s="7"/>
+      <c r="A859" s="3">
+        <v>46149.0</v>
+      </c>
+      <c r="B859" s="6">
+        <v>1684.0</v>
+      </c>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="B860" s="7"/>
+      <c r="A860" s="3">
+        <v>46150.0</v>
+      </c>
+      <c r="B860" s="6">
+        <v>3728.0</v>
+      </c>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="B861" s="7"/>
+      <c r="A861" s="3">
+        <v>46151.0</v>
+      </c>
+      <c r="B861" s="6">
+        <v>3755.0</v>
+      </c>
     </row>
     <row r="862" ht="15.75" customHeight="1">
+      <c r="A862" s="3"/>
       <c r="B862" s="7"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7200,28 +7200,63 @@
       </c>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="3"/>
-      <c r="B862" s="7"/>
+      <c r="A862" s="3">
+        <v>46152.0</v>
+      </c>
+      <c r="B862" s="6">
+        <v>4801.0</v>
+      </c>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="B863" s="7"/>
+      <c r="A863" s="3">
+        <v>46153.0</v>
+      </c>
+      <c r="B863" s="6">
+        <v>1107.0</v>
+      </c>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="B864" s="7"/>
+      <c r="A864" s="3">
+        <v>46154.0</v>
+      </c>
+      <c r="B864" s="6">
+        <v>2455.0</v>
+      </c>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="B865" s="7"/>
+      <c r="A865" s="3">
+        <v>46155.0</v>
+      </c>
+      <c r="B865" s="6">
+        <v>1163.0</v>
+      </c>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="B866" s="7"/>
+      <c r="A866" s="3">
+        <v>46156.0</v>
+      </c>
+      <c r="B866" s="6">
+        <v>2067.0</v>
+      </c>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="B867" s="7"/>
+      <c r="A867" s="3">
+        <v>46157.0</v>
+      </c>
+      <c r="B867" s="6">
+        <v>3990.0</v>
+      </c>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="B868" s="7"/>
+      <c r="A868" s="3">
+        <v>46158.0</v>
+      </c>
+      <c r="B868" s="6">
+        <v>3686.0</v>
+      </c>
     </row>
     <row r="869" ht="15.75" customHeight="1">
+      <c r="A869" s="3"/>
       <c r="B869" s="7"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7256,26 +7256,60 @@
       </c>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="3"/>
-      <c r="B869" s="7"/>
+      <c r="A869" s="3">
+        <v>46159.0</v>
+      </c>
+      <c r="B869" s="6">
+        <v>3560.0</v>
+      </c>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="B870" s="7"/>
+      <c r="A870" s="3">
+        <v>46160.0</v>
+      </c>
+      <c r="B870" s="6">
+        <v>1149.18</v>
+      </c>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="B871" s="7"/>
+      <c r="A871" s="3">
+        <v>46161.0</v>
+      </c>
+      <c r="B871" s="6">
+        <v>2145.0</v>
+      </c>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="B872" s="7"/>
+      <c r="A872" s="3">
+        <v>46162.0</v>
+      </c>
+      <c r="B872" s="6">
+        <v>1281.0</v>
+      </c>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="B873" s="7"/>
+      <c r="A873" s="3">
+        <v>46163.0</v>
+      </c>
+      <c r="B873" s="6">
+        <v>1825.0</v>
+      </c>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="B874" s="7"/>
+      <c r="A874" s="3">
+        <v>46164.0</v>
+      </c>
+      <c r="B874" s="6">
+        <v>4009.0</v>
+      </c>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="B875" s="7"/>
+      <c r="A875" s="3">
+        <v>46165.0</v>
+      </c>
+      <c r="B875" s="6">
+        <v>4597.0</v>
+      </c>
     </row>
     <row r="876" ht="15.75" customHeight="1">
       <c r="B876" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7312,25 +7312,60 @@
       </c>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="B876" s="7"/>
+      <c r="A876" s="3">
+        <v>46166.0</v>
+      </c>
+      <c r="B876" s="6">
+        <v>3329.0</v>
+      </c>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="B877" s="7"/>
+      <c r="A877" s="3">
+        <v>46167.0</v>
+      </c>
+      <c r="B877" s="6">
+        <v>1800.0</v>
+      </c>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="B878" s="7"/>
+      <c r="A878" s="3">
+        <v>46168.0</v>
+      </c>
+      <c r="B878" s="6">
+        <v>1932.0</v>
+      </c>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="B879" s="7"/>
+      <c r="A879" s="3">
+        <v>46169.0</v>
+      </c>
+      <c r="B879" s="6">
+        <v>2201.0</v>
+      </c>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="B880" s="7"/>
+      <c r="A880" s="3">
+        <v>46170.0</v>
+      </c>
+      <c r="B880" s="6">
+        <v>2256.0</v>
+      </c>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="B881" s="7"/>
+      <c r="A881" s="3">
+        <v>46171.0</v>
+      </c>
+      <c r="B881" s="6">
+        <v>4598.0</v>
+      </c>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="B882" s="7"/>
+      <c r="A882" s="3">
+        <v>46172.0</v>
+      </c>
+      <c r="B882" s="6">
+        <v>4687.0</v>
+      </c>
     </row>
     <row r="883" ht="15.75" customHeight="1">
       <c r="B883" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7368,27 +7368,63 @@
       </c>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="B883" s="7"/>
+      <c r="A883" s="3">
+        <v>46173.0</v>
+      </c>
+      <c r="B883" s="6">
+        <v>4078.0</v>
+      </c>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="B884" s="7"/>
+      <c r="A884" s="3">
+        <v>46174.0</v>
+      </c>
+      <c r="B884" s="6">
+        <v>1841.0</v>
+      </c>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="B885" s="7"/>
+      <c r="A885" s="3">
+        <v>46175.0</v>
+      </c>
+      <c r="B885" s="6">
+        <v>1941.0</v>
+      </c>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="B886" s="7"/>
+      <c r="A886" s="3">
+        <v>46176.0</v>
+      </c>
+      <c r="B886" s="6">
+        <v>2430.0</v>
+      </c>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="B887" s="7"/>
+      <c r="A887" s="3">
+        <v>46177.0</v>
+      </c>
+      <c r="B887" s="6">
+        <v>2959.0</v>
+      </c>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="B888" s="7"/>
+      <c r="A888" s="3">
+        <v>46178.0</v>
+      </c>
+      <c r="B888" s="6">
+        <v>4052.0</v>
+      </c>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="B889" s="7"/>
+      <c r="A889" s="3">
+        <v>46179.0</v>
+      </c>
+      <c r="B889" s="6">
+        <v>3737.0</v>
+      </c>
     </row>
     <row r="890" ht="15.75" customHeight="1">
+      <c r="A890" s="3"/>
       <c r="B890" s="7"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7424,26 +7424,60 @@
       </c>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="3"/>
-      <c r="B890" s="7"/>
+      <c r="A890" s="3">
+        <v>46180.0</v>
+      </c>
+      <c r="B890" s="6">
+        <v>3826.0</v>
+      </c>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="B891" s="7"/>
+      <c r="A891" s="3">
+        <v>46181.0</v>
+      </c>
+      <c r="B891" s="6">
+        <v>2000.0</v>
+      </c>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="B892" s="7"/>
+      <c r="A892" s="3">
+        <v>46182.0</v>
+      </c>
+      <c r="B892" s="6">
+        <v>1877.0</v>
+      </c>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="B893" s="7"/>
+      <c r="A893" s="3">
+        <v>46183.0</v>
+      </c>
+      <c r="B893" s="6">
+        <v>1569.56</v>
+      </c>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="B894" s="7"/>
+      <c r="A894" s="3">
+        <v>46184.0</v>
+      </c>
+      <c r="B894" s="6">
+        <v>2366.0</v>
+      </c>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="B895" s="7"/>
+      <c r="A895" s="3">
+        <v>46185.0</v>
+      </c>
+      <c r="B895" s="6">
+        <v>4250.0</v>
+      </c>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="B896" s="7"/>
+      <c r="A896" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B896" s="6">
+        <v>3881.0</v>
+      </c>
     </row>
     <row r="897" ht="15.75" customHeight="1">
       <c r="B897" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7480,25 +7480,60 @@
       </c>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="B897" s="7"/>
+      <c r="A897" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B897" s="6">
+        <v>4040.0</v>
+      </c>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="B898" s="7"/>
+      <c r="A898" s="3">
+        <v>46188.0</v>
+      </c>
+      <c r="B898" s="6">
+        <v>1969.0</v>
+      </c>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="B899" s="7"/>
+      <c r="A899" s="3">
+        <v>46189.0</v>
+      </c>
+      <c r="B899" s="6">
+        <v>2213.0</v>
+      </c>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="B900" s="7"/>
+      <c r="A900" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B900" s="6">
+        <v>2047.0</v>
+      </c>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="B901" s="7"/>
+      <c r="A901" s="3">
+        <v>46191.0</v>
+      </c>
+      <c r="B901" s="6">
+        <v>1830.0</v>
+      </c>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="B902" s="7"/>
+      <c r="A902" s="3">
+        <v>46192.0</v>
+      </c>
+      <c r="B902" s="6">
+        <v>4659.0</v>
+      </c>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="B903" s="7"/>
+      <c r="A903" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B903" s="6">
+        <v>3855.0</v>
+      </c>
     </row>
     <row r="904" ht="15.75" customHeight="1">
       <c r="B904" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7536,46 +7536,116 @@
       </c>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="B904" s="7"/>
+      <c r="A904" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B904" s="6">
+        <v>3732.0</v>
+      </c>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="B905" s="7"/>
+      <c r="A905" s="3">
+        <v>46195.0</v>
+      </c>
+      <c r="B905" s="6">
+        <v>1797.0</v>
+      </c>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="B906" s="7"/>
+      <c r="A906" s="3">
+        <v>46196.0</v>
+      </c>
+      <c r="B906" s="6">
+        <v>4235.0</v>
+      </c>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="B907" s="7"/>
+      <c r="A907" s="3">
+        <v>46197.0</v>
+      </c>
+      <c r="B907" s="6">
+        <v>4080.0</v>
+      </c>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="B908" s="7"/>
+      <c r="A908" s="3">
+        <v>46198.0</v>
+      </c>
+      <c r="B908" s="6">
+        <v>2447.0</v>
+      </c>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="B909" s="7"/>
+      <c r="A909" s="3">
+        <v>46199.0</v>
+      </c>
+      <c r="B909" s="6">
+        <v>3305.0</v>
+      </c>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="B910" s="7"/>
+      <c r="A910" s="3">
+        <v>46200.0</v>
+      </c>
+      <c r="B910" s="6">
+        <v>3490.0</v>
+      </c>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="B911" s="7"/>
+      <c r="A911" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B911" s="6">
+        <v>3572.0</v>
+      </c>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="B912" s="7"/>
+      <c r="A912" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="B912" s="6">
+        <v>2053.0</v>
+      </c>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="B913" s="7"/>
+      <c r="A913" s="3">
+        <v>46203.0</v>
+      </c>
+      <c r="B913" s="6">
+        <v>2741.0</v>
+      </c>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="B914" s="7"/>
+      <c r="A914" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="B914" s="6">
+        <v>2309.0</v>
+      </c>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="B915" s="7"/>
+      <c r="A915" s="3">
+        <v>46205.0</v>
+      </c>
+      <c r="B915" s="6">
+        <v>3964.0</v>
+      </c>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="B916" s="7"/>
+      <c r="A916" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B916" s="6">
+        <v>4163.0</v>
+      </c>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="B917" s="7"/>
+      <c r="A917" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B917" s="6">
+        <v>4515.0</v>
+      </c>
     </row>
     <row r="918" ht="15.75" customHeight="1">
       <c r="B918" s="7"/>

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7648,27 +7648,63 @@
       </c>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="B918" s="7"/>
+      <c r="A918" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B918" s="6">
+        <v>4404.0</v>
+      </c>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="B919" s="7"/>
+      <c r="A919" s="3">
+        <v>46209.0</v>
+      </c>
+      <c r="B919" s="6">
+        <v>3907.0</v>
+      </c>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="B920" s="7"/>
+      <c r="A920" s="3">
+        <v>46210.0</v>
+      </c>
+      <c r="B920" s="6">
+        <v>2277.0</v>
+      </c>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="B921" s="7"/>
+      <c r="A921" s="3">
+        <v>46211.0</v>
+      </c>
+      <c r="B921" s="6">
+        <v>1868.0</v>
+      </c>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="B922" s="7"/>
+      <c r="A922" s="3">
+        <v>46212.0</v>
+      </c>
+      <c r="B922" s="6">
+        <v>2461.0</v>
+      </c>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="B923" s="7"/>
+      <c r="A923" s="3">
+        <v>46213.0</v>
+      </c>
+      <c r="B923" s="6">
+        <v>5879.0</v>
+      </c>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="B924" s="7"/>
+      <c r="A924" s="3">
+        <v>46214.0</v>
+      </c>
+      <c r="B924" s="6">
+        <v>4373.0</v>
+      </c>
     </row>
     <row r="925" ht="15.75" customHeight="1">
+      <c r="A925" s="3"/>
       <c r="B925" s="7"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">

--- a/venta.xlsx
+++ b/venta.xlsx
@@ -7704,28 +7704,63 @@
       </c>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="3"/>
-      <c r="B925" s="7"/>
+      <c r="A925" s="3">
+        <v>46215.0</v>
+      </c>
+      <c r="B925" s="6">
+        <v>3273.0</v>
+      </c>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="B926" s="7"/>
+      <c r="A926" s="3">
+        <v>46216.0</v>
+      </c>
+      <c r="B926" s="6">
+        <v>1976.0</v>
+      </c>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="B927" s="7"/>
+      <c r="A927" s="3">
+        <v>46217.0</v>
+      </c>
+      <c r="B927" s="6">
+        <v>5256.0</v>
+      </c>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="B928" s="7"/>
+      <c r="A928" s="3">
+        <v>46218.0</v>
+      </c>
+      <c r="B928" s="6">
+        <v>2369.0</v>
+      </c>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="B929" s="7"/>
+      <c r="A929" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="B929" s="6">
+        <v>1786.0</v>
+      </c>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="B930" s="7"/>
+      <c r="A930" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="B930" s="6">
+        <v>3484.0</v>
+      </c>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="B931" s="7"/>
+      <c r="A931" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="B931" s="6">
+        <v>4256.0</v>
+      </c>
     </row>
     <row r="932" ht="15.75" customHeight="1">
+      <c r="A932" s="3"/>
       <c r="B932" s="7"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
